--- a/Marketing.Mvc/DadosApp/Relatorio/BaseV1.xlsx
+++ b/Marketing.Mvc/DadosApp/Relatorio/BaseV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projeto\Marketing\Marketing.Mvc\DadosApp\Relatorio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7629465A-CC91-4F4F-B21E-9C88E505CE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F9FE5A-FDC6-4784-9ED0-137F7FFB233A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,7 +113,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -124,6 +124,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,6 +409,7 @@
   <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="16" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="16" style="6"/>
     <col min="2" max="2" width="16" style="3"/>
     <col min="3" max="3" width="32" style="3" customWidth="1"/>
     <col min="4" max="4" width="24.140625" style="3" customWidth="1"/>
@@ -422,7 +424,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
